--- a/risk/beta_report_2026-08-10.xlsx
+++ b/risk/beta_report_2026-08-10.xlsx
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-10 07:31</t>
+          <t>Generated 2026-08-10 08:12</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>19910.9</v>
+        <v>24804.01</v>
       </c>
     </row>
     <row r="5">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>15915.51</v>
+        <v>24804.01</v>
       </c>
     </row>
     <row r="6">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3995.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>0.7993365443048783</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.2006634556951217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9"/>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>0.7377029857323411</v>
+        <v>0.992471552880056</v>
       </c>
     </row>
     <row r="13">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.666110820830943</v>
+        <v>1.554747142587806</v>
       </c>
     </row>
     <row r="14">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.5896729553386805</v>
+        <v>0.992471552880056</v>
       </c>
     </row>
     <row r="15">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.5324467216470919</v>
+        <v>1.554747142587806</v>
       </c>
     </row>
     <row r="16">
@@ -679,11 +679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -715,170 +715,261 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>0.07613467999939733</v>
+        <v>0.07014994752864556</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>1515.91</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>0.07533411347553351</v>
+        <v>0.06434443462972317</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1499.97</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>0.07269485558161611</v>
+        <v>0.06299384655948775</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1447.42</v>
+        <v>1562.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.07262655128597903</v>
+        <v>0.06111552124031558</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1446.06</v>
+        <v>1515.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.07182397581224353</v>
+        <v>0.06047288321525431</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1430.08</v>
+        <v>1499.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>RSP</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.06632246658865244</v>
+        <v>0.05835427416776561</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1320.54</v>
+        <v>1447.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>0.06523210904579903</v>
+        <v>0.05829944432372023</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1298.83</v>
+        <v>1446.06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.06377260696402473</v>
+        <v>0.05765519365618704</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>1269.77</v>
+        <v>1430.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>0.06228045944683564</v>
+        <v>0.05323897224682621</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1240.06</v>
+        <v>1320.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>0.06058189233033162</v>
+        <v>0.05236371054519007</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1206.24</v>
+        <v>1298.83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>0.05791450913821073</v>
+        <v>0.05200771971951309</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1153.13</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>0.05461832463625452</v>
+        <v>0.05119212578933809</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1087.5</v>
+        <v>1269.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>0.04999433559331736</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>1240.06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>TWST</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>0.04958875601162876</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>0.04863084638330657</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>1206.24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>XLV</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>0.04648966034121096</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>1153.13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>0.04384371720540348</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>1087.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>IONQ</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>0.0354781343823035</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>0.02378647646086257</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>0.2006634556951217</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>3995.39</v>
+      <c r="B23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -895,14 +986,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -968,337 +1059,533 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>0.0908585398771387</v>
+        <v>0.07014994752864556</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1.510200255901068</v>
+        <v>3.680339939907058</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1.492718289607255</v>
+        <v>1.683421813106278</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>-0.01748196629381282</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>0.002217540766010997</v>
+        <v>-1.99691812680078</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0.1826213043417158</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0.1372145901732523</v>
+        <v>0.2581756536720586</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>0.1356262042416151</v>
+        <v>0.1180919518579828</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>0.08160781526950753</v>
+        <v>0.06299384655948775</v>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1.421718198588823</v>
+        <v>4.431943457987849</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>1.276085376097083</v>
+        <v>1.521426694909841</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>-0.1456328224917396</v>
+        <v>-2.910516763078008</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0.03296824893229068</v>
+        <v>0.3488645661377751</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0.1160233161157336</v>
+        <v>0.2791851661528121</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>0.1041385396406508</v>
+        <v>0.09584051977065908</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.09424580173679636</v>
+        <v>0.05829944432372023</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1.018180086444278</v>
+        <v>1.510360074093652</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1.01116672751026</v>
+        <v>1.492854171740635</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>-0.007013358934017555</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>0.03925366075005672</v>
+        <v>-0.0175059023530173</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0.002219964768076213</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0.09595919855938161</v>
+        <v>0.08805315304839281</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>0.0952982189237772</v>
+        <v>0.0870325686688266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.07579021972905674</v>
+        <v>0.05200771971951309</v>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1.13549005256219</v>
+        <v>4.394458240321478</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1.128239118211604</v>
+        <v>1.561821766120545</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.007250934350586435</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.003533893582797936</v>
+        <v>-2.832636474200933</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>0.3151173384755841</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0.0860590405838466</v>
+        <v>0.2285457524817441</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>0.08550949067617469</v>
+        <v>0.08122678866423225</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>TWST</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.09524734048736107</v>
+        <v>0.04958875601162876</v>
       </c>
       <c r="C9" s="14" t="n">
-        <v>0.797110096872642</v>
+        <v>2.585841752520523</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>0.8926929324702738</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>0.09558283559763181</v>
+        <v>1.531025453474779</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-1.054816299045744</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.05567133053185986</v>
+        <v>0.1241485097540436</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0.0759226168027419</v>
+        <v>0.1282286757504227</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>0.08502662768965699</v>
+        <v>0.07592164765995407</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>0.07978192341935633</v>
+        <v>0.05236371054519007</v>
       </c>
       <c r="C10" s="14" t="n">
-        <v>0.9574855722450176</v>
+        <v>1.420086037403139</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>0.9607677054900045</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0.003282133244986829</v>
+        <v>1.27474659116113</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.1453394462420099</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0.005228685458593564</v>
+        <v>0.03306215866677791</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0.07639004059999058</v>
+        <v>0.07436097421184396</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>0.07665189550319423</v>
+        <v>0.06675046151802913</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.08985448785492892</v>
+        <v>0.06047288321525431</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>0.6986862244230758</v>
+        <v>1.015489186260007</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>0.7497173295299313</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>0.05103110510685549</v>
+        <v>1.00953408509854</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.005955101161466692</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.01274336758189535</v>
+        <v>0.03903823164413119</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>0.06278009286682941</v>
+        <v>0.06140955896705504</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>0.06736546668087695</v>
+        <v>0.06104943682998264</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>RSP</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>0.08297189345487514</v>
+        <v>0.0354781343823035</v>
       </c>
       <c r="C12" s="14" t="n">
-        <v>0.6465263290425507</v>
+        <v>3.774224069845172</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>0.6564163564459674</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>0.009890027403416712</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0.001799057447320934</v>
+        <v>1.67571582214495</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>-2.098508247700222</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>0.1941004800878098</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>0.05364351368909007</v>
+        <v>0.1339024287388914</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>0.05446410798907215</v>
+        <v>0.05945127112461072</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>0.09094399111307146</v>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>-0.03938624411788774</v>
+        <v>0.06434443462972317</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0.828041332645349</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>0.2354405208391426</v>
+        <v>0.8714439015044244</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>0.2748267649570303</v>
+        <v>0.04340256885907545</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.02246610404813325</v>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>-0.003581942235034445</v>
+        <v>0.02110098692661845</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0.05327985139910751</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>0.0214119006348519</v>
+        <v>0.05607256515382236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>0.06832957285063437</v>
+        <v>0.04863084638330657</v>
       </c>
       <c r="C14" s="14" t="n">
-        <v>0.1456170848447877</v>
+        <v>1.136124400082165</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>0.3131111279254228</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>0.1674940430806351</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>0.01524027847608385</v>
+        <v>1.128829874364436</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>-0.007294525717729039</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>0.003538836466364886</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0.009949953207198929</v>
+        <v>0.0552506911727221</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>0.02139474962592448</v>
+        <v>0.05489595221310414</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>0.07245322330230071</v>
+        <v>0.06111552124031558</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>0.1256987687035761</v>
+        <v>0.7984071853506062</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>0.2276189260862498</v>
+        <v>0.8933313003807209</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>0.1019201573826737</v>
+        <v>0.09492411503011478</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.008247237084849163</v>
+        <v>0.05561853862058238</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0.009107280957704446</v>
+        <v>0.04879507129471555</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>0.01649172487955693</v>
+        <v>0.05459640806305669</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
+          <t>XLI</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>0.05119212578933809</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0.9575788393687121</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>0.9608533851602322</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0.003274545791520089</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>0.005228015571913439</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0.04902049639817149</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0.04918812735823393</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>0.05765519365618704</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0.6984942645579427</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>0.7495942612716507</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0.05109999671370802</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0.01275429952534538</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0.04027182209082413</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0.04321800229718348</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>RSP</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>0.05323897224682621</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>0.6467347773282435</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>0.6565955118575909</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>0.009860734529347437</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>0.001794664686585669</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>0.03443149486123569</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>0.03495647023317693</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>0.02378647646086257</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>1.951681248378986</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>1.372908886183973</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>-0.5787723621950134</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0.09700297841479273</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>0.04642362007367364</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>0.03265666490412412</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>0.04384371720540348</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0.1462098229739192</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0.3134039612307944</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>0.1671941382568753</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0.01521947848663204</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0.006410382131120617</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>0.01374079464725619</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>MRK</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>0.05835427416776561</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>-0.04023901993090227</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>0.2351645177741342</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>0.2754035377050365</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0.02250512888925</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>-0.002348118801290056</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0.01372285474472222</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>XLV</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>0.04648966034121096</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>0.1245656033891221</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>0.2269853866224489</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>0.1024197832333268</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>0.008280873791135525</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0.005791012591758282</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>0.0105524735264961</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
           <t>CVX</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>0.07791519090497255</v>
-      </c>
-      <c r="C16" s="15" t="n">
-        <v>-0.6848071585278844</v>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>-0.3295370319290553</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>0.3552701265988291</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>0.01670083824608479</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>-0.05335688048979192</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>-0.02567594075301038</v>
+      <c r="B23" s="12" t="n">
+        <v>0.04999433559331736</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>-0.6888889158886415</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>-0.3299055014864946</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>0.3589834144021469</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.01687072004368427</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>-0.03444054364745332</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-0.01649340635539747</v>
       </c>
     </row>
   </sheetData>
